--- a/data/file_generation/input/data_84/伯威逊面料管理-扩展颜色-1119-1.xlsx
+++ b/data/file_generation/input/data_84/伯威逊面料管理-扩展颜色-1119-1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenguanzhou/Downloads/澳鹏-数值统计数据编辑/xh组汇总/input/7dbbe4b7-caab-41a4-885c-d3ca348c9b07/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenguanzhou/Desktop/new_input/data_84/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF8D098-BEBB-9748-912D-99D07460D9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978A88C0-9072-2F49-86C8-C95E06AFED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="面料模板" sheetId="1" r:id="rId1"/>
@@ -7596,13 +7596,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C9B9C5B-EEE6-4738-9492-54AB6BDCA3E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B4571CB-37A1-4AFA-B70A-75DC0DF17ACD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9570420-AAD7-4A02-A267-9A61CA927C96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101EECFD-2B06-4C91-A8AB-4606C7BE9E66}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{967C40E1-C6BD-4CAF-A5F2-74F1296528FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45401D62-1B1A-4EF0-A63C-F3A4184F9411}"/>
 </file>